--- a/Дело3а-78-2026Таганай/11_Поставщики/15. ООО Будь здоров/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/15. ООО Будь здоров/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92539426147</v>
+        <v>46157.93113315553</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/15. ООО Будь здоров/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/15. ООО Будь здоров/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93113315553</v>
+        <v>46157.93367867353</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/15. ООО Будь здоров/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/15. ООО Будь здоров/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93367867353</v>
+        <v>46157.93671357611</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/15. ООО Будь здоров/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/15. ООО Будь здоров/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93671357611</v>
+        <v>46158.28193887224</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/15. ООО Будь здоров/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/15. ООО Будь здоров/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28193887224</v>
+        <v>46158.29717551492</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/15. ООО Будь здоров/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/15. ООО Будь здоров/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29717551492</v>
+        <v>46158.29789817748</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/15. ООО Будь здоров/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/15. ООО Будь здоров/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29789817748</v>
+        <v>46158.33355425856</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/15. ООО Будь здоров/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/15. ООО Будь здоров/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33355425856</v>
+        <v>46158.37210432166</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/15. ООО Будь здоров/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/15. ООО Будь здоров/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37210432166</v>
+        <v>46158.37267471846</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
